--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.85362323218244</v>
+        <v>2.413713775229647</v>
       </c>
       <c r="D2" t="n">
-        <v>15.30981032981128</v>
+        <v>2.487844178594333</v>
       </c>
       <c r="E2" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F2" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.8058717627038</v>
+        <v>4.843454161439368</v>
       </c>
       <c r="D3" t="n">
-        <v>29.54048770918062</v>
+        <v>4.80032925274185</v>
       </c>
       <c r="E3" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F3" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.57671675487252</v>
+        <v>3.993716472666785</v>
       </c>
       <c r="D4" t="n">
-        <v>24.60994023761819</v>
+        <v>3.999115288612956</v>
       </c>
       <c r="E4" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F4" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.89214573156504</v>
+        <v>3.069973681379319</v>
       </c>
       <c r="D5" t="n">
-        <v>18.44451677843544</v>
+        <v>2.997233976495759</v>
       </c>
       <c r="E5" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F5" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.58361927308709</v>
+        <v>5.619838131876653</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01316972163028</v>
+        <v>5.68964007976492</v>
       </c>
       <c r="E6" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F6" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.24085977377984</v>
+        <v>6.214139713239224</v>
       </c>
       <c r="D7" t="n">
-        <v>37.90111393973947</v>
+        <v>6.158931015207664</v>
       </c>
       <c r="E7" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F7" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.34437621879497</v>
+        <v>2.980961135554183</v>
       </c>
       <c r="D8" t="n">
-        <v>18.73097218482793</v>
+        <v>3.04378298003454</v>
       </c>
       <c r="E8" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F8" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.37785947010065</v>
+        <v>4.448902163891356</v>
       </c>
       <c r="D9" t="n">
-        <v>27.26130213786045</v>
+        <v>4.429961597402323</v>
       </c>
       <c r="E9" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F9" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.51244146131699</v>
+        <v>4.795771737464012</v>
       </c>
       <c r="D10" t="n">
-        <v>29.30303760017863</v>
+        <v>4.761743610029027</v>
       </c>
       <c r="E10" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F10" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.06425975407996</v>
+        <v>3.747942210037993</v>
       </c>
       <c r="D11" t="n">
-        <v>22.89291631561036</v>
+        <v>3.720098901286684</v>
       </c>
       <c r="E11" t="n">
-        <v>7.044130705472962</v>
+        <v>1.144671239639356</v>
       </c>
       <c r="F11" t="n">
-        <v>6.954147436431047</v>
+        <v>1.130048958420045</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
